--- a/data/trans_orig/IQ14-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IQ14-Provincia-trans_orig.xlsx
@@ -526,7 +526,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Número de días que los menores se han tenido que quedar en la cama más de medio día por motivos de salud</t>
+          <t>Número de días que los menores se han tenido que quedar en la cama más de medio día por motivos de salud (tasa de respuesta: 97,77%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -638,7 +638,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -716,12 +716,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,37; 5,98</t>
+          <t>1,18; 6,11</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,85; 4,64</t>
+          <t>1,93; 5,04</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -731,7 +731,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,83; 6,57</t>
+          <t>3,91; 6,59</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -741,12 +741,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,12; 2,74</t>
+          <t>1,12; 2,61</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,0; 2,06</t>
+          <t>1,0; 2,07</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -756,29 +756,29 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,32; 4,78</t>
+          <t>1,33; 4,84</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,52; 2,93</t>
+          <t>1,56; 3,02</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,0; 4,04</t>
+          <t>1,0; 3,85</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>5,01; 8,47</t>
+          <t>5,05; 8,36</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -856,69 +856,69 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,1; 5,02</t>
+          <t>2,1; 5,05</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,18; 3,6</t>
+          <t>1,21; 4,18</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,36; 4,7</t>
+          <t>1,33; 4,76</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,62; 9,33</t>
+          <t>1,6; 9,55</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,51; 2,58</t>
+          <t>1,52; 2,6</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,37; 4,73</t>
+          <t>1,4; 4,93</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,34; 4,62</t>
+          <t>2,38; 4,46</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,53; 3,04</t>
+          <t>1,58; 3,05</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,91; 3,42</t>
+          <t>1,9; 3,38</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,42; 3,21</t>
+          <t>1,41; 3,47</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,92; 4,26</t>
+          <t>1,89; 4,13</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,84; 5,17</t>
+          <t>1,88; 5,58</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -1001,7 +1001,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,41; 6,61</t>
+          <t>1,4; 5,81</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,84; 5,07</t>
+          <t>1,84; 5,64</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,37; 4,95</t>
+          <t>1,39; 4,9</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -1031,17 +1031,17 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,0; 10,53</t>
+          <t>1,3; 10,83</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,0; 7,0</t>
+          <t>1,0; 5,49</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,71; 4,66</t>
+          <t>1,62; 4,65</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
@@ -1051,7 +1051,7 @@
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,8; 6,08</t>
+          <t>1,83; 6,37</t>
         </is>
       </c>
     </row>
@@ -1141,12 +1141,12 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,75; 6,42</t>
+          <t>1,0; 6,42</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,0; 3,76</t>
+          <t>1,0; 3,51</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,35; 7,34</t>
+          <t>1,4; 7,3</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,0; 6,92</t>
+          <t>1,0; 7,04</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1176,17 +1176,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,18; 5,38</t>
+          <t>1,18; 5,31</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,59; 5,62</t>
+          <t>1,66; 5,77</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,29; 2,6</t>
+          <t>1,26; 2,57</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1281,7 +1281,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,83; 5,06</t>
+          <t>1,9; 4,93</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1301,17 +1301,17 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,23; 3,3</t>
+          <t>1,35; 3,27</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,0; 2,78</t>
+          <t>1,26; 2,78</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>3,84; 23,73</t>
+          <t>3,97; 24,15</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1321,24 +1321,24 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1,88; 3,83</t>
+          <t>1,93; 4,06</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1,66; 4,0</t>
+          <t>1,72; 4,28</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>4,13; 21,55</t>
+          <t>4,14; 20,89</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1,2; 3,94</t>
+          <t>1,2; 4,1</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1451,17 +1451,17 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>3,02; 9,5</t>
+          <t>2,89; 9,49</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1,0; 2,48</t>
+          <t>1,0; 2,73</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1,46; 5,75</t>
+          <t>1,45; 5,75</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
@@ -1471,14 +1471,14 @@
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>2,33; 6,61</t>
+          <t>2,3; 6,4</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1556,22 +1556,22 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,69; 7,64</t>
+          <t>1,69; 8,43</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,65; 5,85</t>
+          <t>1,65; 6,19</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,03; 5,47</t>
+          <t>2,03; 5,54</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2,37; 4,36</t>
+          <t>2,49; 4,3</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1581,37 +1581,37 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,0; 10,67</t>
+          <t>1,35; 10,67</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,0; 2,75</t>
+          <t>1,0; 2,5</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>3,03; 7,53</t>
+          <t>3,05; 7,46</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1,81; 6,71</t>
+          <t>1,74; 6,5</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1,85; 7,41</t>
+          <t>1,83; 6,95</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1,75; 3,99</t>
+          <t>1,77; 4,51</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>3,09; 5,86</t>
+          <t>3,04; 5,55</t>
         </is>
       </c>
     </row>
@@ -1696,62 +1696,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>2,05; 7,05</t>
+          <t>1,99; 7,31</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1,51; 4,04</t>
+          <t>1,51; 4,06</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2,05; 5,4</t>
+          <t>2,09; 5,36</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3,66; 6,81</t>
+          <t>3,71; 6,86</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>2,23; 3,91</t>
+          <t>2,23; 3,98</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,7; 4,66</t>
+          <t>1,61; 4,63</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,29; 2,63</t>
+          <t>1,28; 2,63</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>4,95; 8,12</t>
+          <t>4,87; 8,19</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>2,4; 4,48</t>
+          <t>2,41; 4,36</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1,72; 3,64</t>
+          <t>1,76; 3,68</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>1,9; 4,28</t>
+          <t>1,9; 4,26</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>4,93; 7,45</t>
+          <t>5,12; 7,57</t>
         </is>
       </c>
     </row>
@@ -1836,62 +1836,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2,08; 4,2</t>
+          <t>2,09; 3,93</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2,04; 3,24</t>
+          <t>2,08; 3,32</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2,23; 3,78</t>
+          <t>2,27; 3,83</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>3,2; 4,7</t>
+          <t>3,18; 4,63</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>2,22; 3,68</t>
+          <t>2,15; 3,5</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,91; 3,3</t>
+          <t>1,92; 3,24</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,58; 2,31</t>
+          <t>1,61; 2,35</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>3,92; 6,65</t>
+          <t>3,99; 6,87</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>2,27; 3,44</t>
+          <t>2,26; 3,4</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>2,13; 3,0</t>
+          <t>2,12; 3,03</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>2,03; 2,9</t>
+          <t>2,01; 2,9</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>3,88; 5,61</t>
+          <t>3,89; 5,5</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ14-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IQ14-Provincia-trans_orig.xlsx
@@ -526,7 +526,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Número de días que los menores se han tenido que quedar en la cama más de medio día por motivos de salud (tasa de respuesta: 97,77%)</t>
+          <t>Tiempo demio en días que en las últimas 2 semanas los menores se han tenido que quedar en la cama más de medio día por motivos de salud (tasa de respuesta: 97,77%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,12 +716,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,18; 6,11</t>
+          <t>1,18; 5,98</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,93; 5,04</t>
+          <t>1,86; 5,04</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -731,7 +731,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,91; 6,59</t>
+          <t>3,9; 6,59</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -741,12 +741,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,12; 2,61</t>
+          <t>1,12; 2,74</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,0; 2,07</t>
+          <t>1,0; 2,06</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -756,22 +756,22 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,33; 4,84</t>
+          <t>1,44; 4,76</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,56; 3,02</t>
+          <t>1,58; 3,08</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,0; 3,85</t>
+          <t>1,0; 3,87</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>5,05; 8,36</t>
+          <t>5,06; 8,52</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,1; 5,05</t>
+          <t>2,1; 5,08</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,21; 4,18</t>
+          <t>1,2; 4,12</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,33; 4,76</t>
+          <t>1,34; 4,99</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,6; 9,55</t>
+          <t>1,59; 9,34</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,52; 2,6</t>
+          <t>1,51; 2,58</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,4; 4,93</t>
+          <t>1,38; 4,39</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,38; 4,46</t>
+          <t>2,33; 4,35</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,58; 3,05</t>
+          <t>1,59; 3,05</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,9; 3,38</t>
+          <t>1,94; 3,54</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,41; 3,47</t>
+          <t>1,4; 3,47</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,89; 4,13</t>
+          <t>1,91; 4,07</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,88; 5,58</t>
+          <t>1,81; 5,45</t>
         </is>
       </c>
     </row>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,4; 5,81</t>
+          <t>1,42; 6,46</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,84; 5,64</t>
+          <t>1,84; 5,23</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,39; 4,9</t>
+          <t>1,37; 4,95</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -1031,7 +1031,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,3; 10,83</t>
+          <t>1,29; 9,78</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,62; 4,65</t>
+          <t>1,67; 4,55</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
@@ -1051,7 +1051,7 @@
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,83; 6,37</t>
+          <t>1,73; 5,98</t>
         </is>
       </c>
     </row>
@@ -1146,7 +1146,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,0; 3,51</t>
+          <t>1,0; 3,76</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1156,17 +1156,17 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,4; 7,3</t>
+          <t>1,25; 7,4</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,0; 7,04</t>
+          <t>1,0; 6,89</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,11; 1,79</t>
+          <t>1,12; 1,79</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1176,22 +1176,22 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,18; 5,31</t>
+          <t>1,17; 5,73</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,66; 5,77</t>
+          <t>1,59; 6,03</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,26; 2,57</t>
+          <t>1,28; 2,48</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2,89; 7,0</t>
+          <t>2,99; 7,0</t>
         </is>
       </c>
     </row>
@@ -1281,12 +1281,12 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,9; 4,93</t>
+          <t>1,8; 4,82</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,68; 5,26</t>
+          <t>1,67; 4,89</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1301,17 +1301,17 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,35; 3,27</t>
+          <t>1,23; 3,24</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,26; 2,78</t>
+          <t>1,0; 2,78</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>3,97; 24,15</t>
+          <t>3,94; 24,24</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1321,17 +1321,17 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1,93; 4,06</t>
+          <t>1,84; 3,86</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1,72; 4,28</t>
+          <t>1,63; 3,93</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>4,14; 20,89</t>
+          <t>4,14; 19,51</t>
         </is>
       </c>
     </row>
@@ -1431,7 +1431,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1,2; 4,1</t>
+          <t>1,31; 4,1</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2,89; 9,49</t>
+          <t>3,04; 9,79</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1461,7 +1461,7 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1,45; 5,75</t>
+          <t>1,46; 5,75</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>2,3; 6,4</t>
+          <t>2,3; 6,12</t>
         </is>
       </c>
     </row>
@@ -1556,22 +1556,22 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,69; 8,43</t>
+          <t>1,79; 8,46</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,65; 6,19</t>
+          <t>1,65; 5,67</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,03; 5,54</t>
+          <t>2,04; 5,38</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2,49; 4,3</t>
+          <t>2,39; 4,33</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1586,32 +1586,32 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,0; 2,5</t>
+          <t>1,0; 2,56</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>3,05; 7,46</t>
+          <t>3,03; 8,76</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1,74; 6,5</t>
+          <t>1,87; 6,76</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1,83; 6,95</t>
+          <t>1,83; 6,88</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1,77; 4,51</t>
+          <t>1,8; 4,09</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>3,04; 5,55</t>
+          <t>3,02; 5,87</t>
         </is>
       </c>
     </row>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>1,99; 7,31</t>
+          <t>1,86; 6,71</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1706,52 +1706,52 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2,09; 5,36</t>
+          <t>2,11; 5,48</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3,71; 6,86</t>
+          <t>3,76; 6,92</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>2,23; 3,98</t>
+          <t>2,25; 3,92</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,61; 4,63</t>
+          <t>1,65; 4,65</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,28; 2,63</t>
+          <t>1,29; 2,63</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>4,87; 8,19</t>
+          <t>4,99; 8,18</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>2,41; 4,36</t>
+          <t>2,37; 4,29</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1,76; 3,68</t>
+          <t>1,72; 3,81</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>1,9; 4,26</t>
+          <t>1,86; 4,06</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>5,12; 7,57</t>
+          <t>4,97; 7,4</t>
         </is>
       </c>
     </row>
@@ -1836,62 +1836,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2,09; 3,93</t>
+          <t>2,03; 3,92</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2,08; 3,32</t>
+          <t>2,03; 3,23</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2,27; 3,83</t>
+          <t>2,26; 3,87</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>3,18; 4,63</t>
+          <t>3,25; 4,72</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>2,15; 3,5</t>
+          <t>2,14; 3,6</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,92; 3,24</t>
+          <t>1,94; 3,29</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,61; 2,35</t>
+          <t>1,62; 2,28</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>3,99; 6,87</t>
+          <t>3,97; 6,69</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>2,26; 3,4</t>
+          <t>2,27; 3,39</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>2,12; 3,03</t>
+          <t>2,12; 3,0</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>2,01; 2,9</t>
+          <t>2,04; 2,98</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>3,89; 5,5</t>
+          <t>3,88; 5,51</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ14-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IQ14-Provincia-trans_orig.xlsx
@@ -526,13 +526,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Tiempo demio en días que en las últimas 2 semanas los menores se han tenido que quedar en la cama más de medio día por motivos de salud (tasa de respuesta: 97,77%)</t>
+          <t>Tiempo medio en días que en las últimas 2 semanas los menores se han tenido que quedar en la cama más de medio día por motivos de salud (tasa de respuesta: 97,77%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -540,7 +540,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -648,42 +648,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>2,31</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1,68</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1,27</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>8,66</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>2,82</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>2,78</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>4,59</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>5,39</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>2,31</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>1,68</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>1,27</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>8,69</t>
+          <t>5,37</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>6,54</t>
+          <t>6,47</t>
         </is>
       </c>
     </row>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,18; 5,98</t>
+          <t>1,0; 5,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,86; 5,04</t>
+          <t>1,12; 2,74</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
+          <t>1,0; 2,06</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>7,0; 10,0</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>1,37; 5,98</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>1,85; 4,64</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
           <t>1,0; 7,0</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>3,9; 6,59</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>1,0; 5,0</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>1,12; 2,74</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>1,0; 2,06</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>7,0; 10,0</t>
+          <t>3,78; 6,55</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,44; 4,76</t>
+          <t>1,32; 4,78</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,58; 3,08</t>
+          <t>1,52; 2,93</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,0; 3,87</t>
+          <t>1,0; 4,04</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>5,06; 8,52</t>
+          <t>4,91; 8,32</t>
         </is>
       </c>
     </row>
@@ -788,42 +788,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>1,98</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>2,13</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>3,18</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>2,19</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>2,95</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>1,87</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>2,15</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>3,7</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>1,98</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>2,13</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>3,18</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2,18</t>
+          <t>3,78</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2,76</t>
+          <t>2,84</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,1; 5,08</t>
+          <t>1,51; 2,58</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,2; 4,12</t>
+          <t>1,37; 4,73</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,34; 4,99</t>
+          <t>2,34; 4,62</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,59; 9,34</t>
+          <t>1,51; 3,05</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,51; 2,58</t>
+          <t>2,1; 5,02</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,38; 4,39</t>
+          <t>1,18; 3,6</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,33; 4,35</t>
+          <t>1,36; 4,7</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,59; 3,05</t>
+          <t>1,58; 9,46</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,94; 3,54</t>
+          <t>1,91; 3,42</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,4; 3,47</t>
+          <t>1,42; 3,21</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,91; 4,07</t>
+          <t>1,92; 4,26</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,81; 5,45</t>
+          <t>1,81; 5,4</t>
         </is>
       </c>
     </row>
@@ -928,42 +928,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>3,99</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>2,34</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
           <t>1,0</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>3,19</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>1,0</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>2,94</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>3,48</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>2,76</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>3,99</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>2,34</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>1,0</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>3,2</t>
+          <t>2,98</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>2,97</t>
+          <t>3,08</t>
         </is>
       </c>
     </row>
@@ -996,52 +996,52 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>1,0; 7,0</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>1,37; 4,95</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>1,42; 6,46</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>1,0; 9,25</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>1,41; 6,61</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
         <is>
           <t>3,0; 4,0</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>1,84; 5,23</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>1,83; 5,7</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>1,0; 7,0</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>1,37; 4,95</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>1,29; 9,78</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>1,0; 5,49</t>
-        </is>
-      </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,67; 4,55</t>
+          <t>1,71; 4,66</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
@@ -1051,7 +1051,7 @@
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,73; 5,98</t>
+          <t>1,79; 5,81</t>
         </is>
       </c>
     </row>
@@ -1068,42 +1068,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>2,92</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>3,1</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1,41</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>4,74</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>1,0</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>3,62</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>2,52</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>5,53</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>2,92</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>3,1</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>1,41</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>4,81</t>
+          <t>5,27</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>5,19</t>
+          <t>5,03</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>1,35; 7,34</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>1,0; 6,92</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>1,11; 1,79</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>2,0; 7,0</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>1,0; 6,42</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>1,75; 6,42</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>1,0; 3,76</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="J11" s="2" t="inlineStr">
         <is>
           <t>3,0; 7,0</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>1,25; 7,4</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>1,0; 6,89</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>1,12; 1,79</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>2,0; 7,0</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,17; 5,73</t>
+          <t>1,18; 5,38</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,59; 6,03</t>
+          <t>1,59; 5,62</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,28; 2,48</t>
+          <t>1,29; 2,6</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2,99; 7,0</t>
+          <t>2,8; 7,0</t>
         </is>
       </c>
     </row>
@@ -1208,42 +1208,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>2,0</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>2,12</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>1,81</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>10,35</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>1,0</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>3,04</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>2,59</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>4,47</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>2,0</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>2,12</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>1,81</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>10,74</t>
+          <t>4,44</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>8,14</t>
+          <t>7,91</t>
         </is>
       </c>
     </row>
@@ -1281,17 +1281,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,8; 4,82</t>
+          <t>1,23; 3,3</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,67; 4,89</t>
+          <t>1,0; 2,78</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3,0; 6,0</t>
+          <t>3,67; 21,35</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1301,17 +1301,17 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,23; 3,24</t>
+          <t>1,83; 5,06</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,0; 2,78</t>
+          <t>1,68; 5,26</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>3,94; 24,24</t>
+          <t>3,0; 6,04</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1321,17 +1321,17 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1,84; 3,86</t>
+          <t>1,88; 3,83</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1,63; 3,93</t>
+          <t>1,66; 4,0</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>4,14; 19,51</t>
+          <t>4,06; 20,9</t>
         </is>
       </c>
     </row>
@@ -1348,62 +1348,62 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>1,96</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>4,5</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>2,0</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>5,49</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>1,43</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>1,47</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>2,17</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>1,96</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>4,5</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>2,14</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>1,67</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>2,87</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>2,0</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>5,22</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>1,67</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>2,87</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>2,0</t>
-        </is>
-      </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>3,68</t>
+          <t>3,64</t>
         </is>
       </c>
     </row>
@@ -1416,62 +1416,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>1,0; 3,0</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>2,0; 7,0</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>2,89; 10,18</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
           <t>1,0; 2,0</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="H15" s="2" t="inlineStr">
         <is>
           <t>1,0; 2,0</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="I15" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>1,31; 4,1</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>1,0; 3,0</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>2,0; 7,0</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>1,17; 3,9</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>1,0; 2,48</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>1,46; 5,75</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>3,04; 9,79</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>1,0; 2,73</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>1,46; 5,75</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>2,3; 6,12</t>
+          <t>2,18; 6,67</t>
         </is>
       </c>
     </row>
@@ -1488,42 +1488,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>3,19</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>4,08</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>1,72</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>4,29</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>3,69</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>3,17</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>3,37</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>3,21</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>3,19</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>4,08</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>1,72</t>
-        </is>
-      </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>4,26</t>
+          <t>3,18</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1543,7 +1543,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>3,83</t>
+          <t>3,82</t>
         </is>
       </c>
     </row>
@@ -1556,62 +1556,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,79; 8,46</t>
+          <t>1,0; 7,77</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,65; 5,67</t>
+          <t>1,0; 10,67</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,04; 5,38</t>
+          <t>1,0; 2,75</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2,39; 4,33</t>
+          <t>2,97; 7,74</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,0; 7,77</t>
+          <t>1,69; 7,64</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,35; 10,67</t>
+          <t>1,65; 5,85</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,0; 2,56</t>
+          <t>2,03; 5,47</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>3,03; 8,76</t>
+          <t>2,36; 4,4</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1,87; 6,76</t>
+          <t>1,81; 6,71</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1,83; 6,88</t>
+          <t>1,85; 7,41</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1,8; 4,09</t>
+          <t>1,75; 3,99</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>3,02; 5,87</t>
+          <t>3,05; 5,99</t>
         </is>
       </c>
     </row>
@@ -1628,44 +1628,44 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>2,96</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>2,53</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>1,76</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>6,87</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
           <t>3,6</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>2,3</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="I18" s="2" t="inlineStr">
         <is>
           <t>3,2</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="J18" s="2" t="inlineStr">
         <is>
           <t>5,45</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>2,96</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>2,53</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>1,76</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>6,7</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
           <t>3,17</t>
@@ -1683,7 +1683,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>6,27</t>
+          <t>6,43</t>
         </is>
       </c>
     </row>
@@ -1696,62 +1696,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>1,86; 6,71</t>
+          <t>2,23; 3,91</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1,51; 4,06</t>
+          <t>1,7; 4,66</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2,11; 5,48</t>
+          <t>1,29; 2,63</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3,76; 6,92</t>
+          <t>5,15; 8,25</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>2,25; 3,92</t>
+          <t>2,05; 7,05</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,65; 4,65</t>
+          <t>1,51; 4,04</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,29; 2,63</t>
+          <t>2,05; 5,4</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>4,99; 8,18</t>
+          <t>3,69; 6,82</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>2,37; 4,29</t>
+          <t>2,4; 4,48</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1,72; 3,81</t>
+          <t>1,72; 3,64</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>1,86; 4,06</t>
+          <t>1,9; 4,28</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>4,97; 7,4</t>
+          <t>5,06; 7,65</t>
         </is>
       </c>
     </row>
@@ -1768,42 +1768,42 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>2,72</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>2,43</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>1,89</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>5,12</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
           <t>2,77</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>2,58</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>2,84</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>3,84</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>2,72</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>2,43</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>1,89</t>
-        </is>
-      </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>5,01</t>
+          <t>3,81</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1823,7 +1823,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>4,5</t>
+          <t>4,54</t>
         </is>
       </c>
     </row>
@@ -1836,62 +1836,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2,03; 3,92</t>
+          <t>2,22; 3,68</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2,03; 3,23</t>
+          <t>1,91; 3,3</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2,26; 3,87</t>
+          <t>1,58; 2,31</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>3,25; 4,72</t>
+          <t>4,0; 6,87</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>2,14; 3,6</t>
+          <t>2,08; 4,2</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,94; 3,29</t>
+          <t>2,04; 3,24</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,62; 2,28</t>
+          <t>2,23; 3,78</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>3,97; 6,69</t>
+          <t>3,17; 4,72</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>2,27; 3,39</t>
+          <t>2,27; 3,44</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>2,12; 3,0</t>
+          <t>2,13; 3,0</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>2,04; 2,98</t>
+          <t>2,03; 2,9</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>3,88; 5,51</t>
+          <t>3,86; 5,59</t>
         </is>
       </c>
     </row>
